--- a/БД/БД.xlsx
+++ b/БД/БД.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dmitr\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\.Git Clone\isp9-51\БД\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38C44FBD-2462-4D4F-83A1-08BC259E8385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A94C3F8-1FB3-4DED-9175-5C77B72A960D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" firstSheet="2" activeTab="2" xr2:uid="{8A7FE3D2-0A56-4277-AE46-CB5CFDB1311B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="2" activeTab="3" xr2:uid="{8A7FE3D2-0A56-4277-AE46-CB5CFDB1311B}"/>
   </bookViews>
   <sheets>
     <sheet name="Supplier" sheetId="1" r:id="rId1"/>
